--- a/data/s3/Kanaleneiland/archetypes/pop_archetypes_citizen.xlsx
+++ b/data/s3/Kanaleneiland/archetypes/pop_archetypes_citizen.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asier.divasson\Documents\GitHub\CogniCity\data\Kanaleneiland\archetypes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asier.divasson\Documents\GitHub\CogniCity\data\s0\Kanaleneiland\archetypes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{801CF929-EC2F-44B9-90FD-D48BD17F04BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6856223F-62AC-40F4-A262-0A110E50AA99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
